--- a/進捗管理表_森数.xlsx
+++ b/進捗管理表_森数.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8F6D090E371E95AA/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9C7F0A8-F68B-4C9B-B2E8-80FB148C5694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F64A686-C2D8-43C0-8371-9E72422517D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1018,26 +1018,44 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1074,24 +1092,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1402,142 +1402,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="52" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="56">
+      <c r="G3" s="62">
         <v>45705</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="58"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
+      <c r="AH3" s="63"/>
+      <c r="AI3" s="63"/>
+      <c r="AJ3" s="63"/>
+      <c r="AK3" s="63"/>
+      <c r="AL3" s="64"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-      <c r="Z4" s="60"/>
-      <c r="AA4" s="60"/>
-      <c r="AB4" s="60"/>
-      <c r="AC4" s="60"/>
-      <c r="AD4" s="60"/>
-      <c r="AE4" s="60"/>
-      <c r="AF4" s="60"/>
-      <c r="AG4" s="60"/>
-      <c r="AH4" s="60"/>
-      <c r="AI4" s="60"/>
-      <c r="AJ4" s="60"/>
-      <c r="AK4" s="60"/>
-      <c r="AL4" s="61"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="66"/>
+      <c r="Y4" s="66"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="67"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="66"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="50">
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="57">
         <v>17</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="52">
+      <c r="H5" s="58"/>
+      <c r="I5" s="54">
         <v>18</v>
       </c>
-      <c r="J5" s="69"/>
-      <c r="K5" s="52">
+      <c r="J5" s="55"/>
+      <c r="K5" s="54">
         <v>19</v>
       </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="52">
+      <c r="L5" s="55"/>
+      <c r="M5" s="54">
         <v>20</v>
       </c>
-      <c r="N5" s="69"/>
-      <c r="O5" s="52">
+      <c r="N5" s="55"/>
+      <c r="O5" s="54">
         <v>21</v>
       </c>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="52">
+      <c r="P5" s="55"/>
+      <c r="Q5" s="54">
         <v>25</v>
       </c>
-      <c r="R5" s="69"/>
-      <c r="S5" s="50">
+      <c r="R5" s="55"/>
+      <c r="S5" s="57">
         <v>26</v>
       </c>
-      <c r="T5" s="51"/>
-      <c r="U5" s="52">
+      <c r="T5" s="58"/>
+      <c r="U5" s="54">
         <v>27</v>
       </c>
-      <c r="V5" s="51"/>
-      <c r="W5" s="52">
+      <c r="V5" s="58"/>
+      <c r="W5" s="54">
         <v>28</v>
       </c>
-      <c r="X5" s="51"/>
+      <c r="X5" s="58"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -1559,43 +1559,43 @@
       <c r="C6" s="47"/>
       <c r="D6" s="47"/>
       <c r="E6" s="47"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="50" t="s">
+      <c r="F6" s="61"/>
+      <c r="G6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="62" t="s">
+      <c r="H6" s="58"/>
+      <c r="I6" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="51"/>
-      <c r="K6" s="52" t="s">
+      <c r="J6" s="58"/>
+      <c r="K6" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52" t="s">
+      <c r="L6" s="58"/>
+      <c r="M6" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="51"/>
-      <c r="O6" s="52" t="s">
+      <c r="N6" s="58"/>
+      <c r="O6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="52" t="s">
+      <c r="P6" s="58"/>
+      <c r="Q6" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="51"/>
-      <c r="S6" s="63" t="s">
+      <c r="R6" s="58"/>
+      <c r="S6" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="51"/>
-      <c r="U6" s="64" t="s">
+      <c r="T6" s="58"/>
+      <c r="U6" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="51"/>
-      <c r="W6" s="64" t="s">
+      <c r="V6" s="58"/>
+      <c r="W6" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="51"/>
+      <c r="X6" s="58"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
@@ -1654,12 +1654,12 @@
       <c r="AL7" s="20"/>
     </row>
     <row r="8" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A8" s="46">
+      <c r="A8" s="49">
         <v>1</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
       <c r="F8" s="21" t="s">
         <v>13</v>
       </c>
@@ -1738,12 +1738,12 @@
       <c r="AL9" s="30"/>
     </row>
     <row r="10" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A10" s="46">
+      <c r="A10" s="49">
         <v>2</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
       <c r="F10" s="31" t="s">
         <v>13</v>
       </c>
@@ -1822,12 +1822,12 @@
       <c r="AL11" s="37"/>
     </row>
     <row r="12" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A12" s="46">
+      <c r="A12" s="49">
         <v>3</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
       <c r="F12" s="21" t="s">
         <v>13</v>
       </c>
@@ -1906,12 +1906,12 @@
       <c r="AL13" s="30"/>
     </row>
     <row r="14" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A14" s="46">
+      <c r="A14" s="49">
         <v>4</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
       <c r="F14" s="31" t="s">
         <v>13</v>
       </c>
@@ -1990,13 +1990,13 @@
       <c r="AL15" s="37"/>
     </row>
     <row r="16" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A16" s="46">
+      <c r="A16" s="49">
         <v>5</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
       <c r="F16" s="21" t="s">
         <v>13</v>
       </c>
@@ -2076,13 +2076,13 @@
       <c r="AL17" s="41"/>
     </row>
     <row r="18" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="49">
         <v>6</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
       <c r="F18" s="31" t="s">
         <v>13</v>
       </c>
@@ -2162,13 +2162,13 @@
       <c r="AL19" s="41"/>
     </row>
     <row r="20" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A20" s="46">
+      <c r="A20" s="49">
         <v>7</v>
       </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
       <c r="F20" s="31" t="s">
         <v>13</v>
       </c>
@@ -2248,13 +2248,13 @@
       <c r="AL21" s="41"/>
     </row>
     <row r="22" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A22" s="46">
+      <c r="A22" s="49">
         <v>8</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
       <c r="F22" s="21" t="s">
         <v>13</v>
       </c>
@@ -2376,19 +2376,19 @@
       <c r="AL24" s="20"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="46">
+      <c r="A25" s="49">
         <v>1</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="46">
         <v>0.5</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="46" t="s">
         <v>40</v>
       </c>
       <c r="F25" s="21" t="s">
@@ -2432,7 +2432,7 @@
       <c r="B26" s="47"/>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
-      <c r="E26" s="49"/>
+      <c r="E26" s="48"/>
       <c r="F26" s="27" t="s">
         <v>14</v>
       </c>
@@ -2470,19 +2470,19 @@
       <c r="AL26" s="30"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="46">
+      <c r="A27" s="49">
         <v>2</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="46">
         <v>1</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="46" t="s">
         <v>39</v>
       </c>
       <c r="F27" s="31" t="s">
@@ -2526,7 +2526,7 @@
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
-      <c r="E28" s="49"/>
+      <c r="E28" s="48"/>
       <c r="F28" s="34" t="s">
         <v>14</v>
       </c>
@@ -2564,19 +2564,19 @@
       <c r="AL28" s="37"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="46">
+      <c r="A29" s="49">
         <v>3</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="46">
         <v>1</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="46" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="21" t="s">
@@ -2620,7 +2620,7 @@
       <c r="B30" s="47"/>
       <c r="C30" s="47"/>
       <c r="D30" s="47"/>
-      <c r="E30" s="49"/>
+      <c r="E30" s="48"/>
       <c r="F30" s="38" t="s">
         <v>14</v>
       </c>
@@ -2658,19 +2658,19 @@
       <c r="AL30" s="30"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="46">
+      <c r="A31" s="49">
         <v>4</v>
       </c>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="46">
         <v>1</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F31" s="31" t="s">
@@ -2678,9 +2678,9 @@
       </c>
       <c r="G31" s="33"/>
       <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="45"/>
       <c r="L31" s="23"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
@@ -2714,7 +2714,7 @@
       <c r="B32" s="47"/>
       <c r="C32" s="47"/>
       <c r="D32" s="47"/>
-      <c r="E32" s="49"/>
+      <c r="E32" s="48"/>
       <c r="F32" s="34" t="s">
         <v>14</v>
       </c>
@@ -2752,15 +2752,15 @@
       <c r="AL32" s="37"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="46">
+      <c r="A33" s="49">
         <v>5</v>
       </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48" t="s">
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="48" t="s">
+      <c r="E33" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F33" s="21" t="s">
@@ -2768,7 +2768,6 @@
       </c>
       <c r="G33" s="25"/>
       <c r="H33" s="24"/>
-      <c r="I33" s="23"/>
       <c r="J33" s="23"/>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
@@ -2804,7 +2803,7 @@
       <c r="B34" s="47"/>
       <c r="C34" s="47"/>
       <c r="D34" s="47"/>
-      <c r="E34" s="49"/>
+      <c r="E34" s="48"/>
       <c r="F34" s="38" t="s">
         <v>14</v>
       </c>
@@ -2842,13 +2841,13 @@
       <c r="AL34" s="41"/>
     </row>
     <row r="35" spans="1:38" ht="12" customHeight="1">
-      <c r="A35" s="46">
+      <c r="A35" s="49">
         <v>6</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
       <c r="F35" s="31" t="s">
         <v>13</v>
       </c>
@@ -2970,19 +2969,19 @@
       <c r="AL37" s="20"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="46">
+      <c r="A38" s="49">
         <v>1</v>
       </c>
-      <c r="B38" s="48" t="s">
+      <c r="B38" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="46">
         <v>3</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="48" t="s">
+      <c r="E38" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -3026,7 +3025,7 @@
       <c r="B39" s="47"/>
       <c r="C39" s="47"/>
       <c r="D39" s="47"/>
-      <c r="E39" s="49"/>
+      <c r="E39" s="48"/>
       <c r="F39" s="27" t="s">
         <v>14</v>
       </c>
@@ -3064,19 +3063,19 @@
       <c r="AL39" s="30"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="46">
+      <c r="A40" s="49">
         <v>2</v>
       </c>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="46">
         <v>1</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F40" s="31" t="s">
@@ -3120,7 +3119,7 @@
       <c r="B41" s="47"/>
       <c r="C41" s="47"/>
       <c r="D41" s="47"/>
-      <c r="E41" s="49"/>
+      <c r="E41" s="48"/>
       <c r="F41" s="34" t="s">
         <v>14</v>
       </c>
@@ -3158,19 +3157,19 @@
       <c r="AL41" s="37"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="46">
+      <c r="A42" s="49">
         <v>3</v>
       </c>
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="48">
+      <c r="C42" s="46">
         <v>4</v>
       </c>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="48" t="s">
+      <c r="E42" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F42" s="21" t="s">
@@ -3211,10 +3210,10 @@
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
       <c r="A43" s="47"/>
-      <c r="B43" s="49"/>
+      <c r="B43" s="48"/>
       <c r="C43" s="47"/>
       <c r="D43" s="47"/>
-      <c r="E43" s="49"/>
+      <c r="E43" s="48"/>
       <c r="F43" s="38" t="s">
         <v>14</v>
       </c>
@@ -3252,19 +3251,19 @@
       <c r="AL43" s="30"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="46">
+      <c r="A44" s="49">
         <v>4</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="46">
         <v>2</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F44" s="31" t="s">
@@ -3307,7 +3306,7 @@
       <c r="B45" s="47"/>
       <c r="C45" s="47"/>
       <c r="D45" s="47"/>
-      <c r="E45" s="49"/>
+      <c r="E45" s="48"/>
       <c r="F45" s="34" t="s">
         <v>14</v>
       </c>
@@ -3345,13 +3344,13 @@
       <c r="AL45" s="37"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="49">
         <v>5</v>
       </c>
-      <c r="B46" s="48"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3431,13 +3430,13 @@
       <c r="AL47" s="41"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="46">
+      <c r="A48" s="49">
         <v>6</v>
       </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
       <c r="F48" s="31" t="s">
         <v>13</v>
       </c>
@@ -3559,19 +3558,19 @@
       <c r="AL50" s="20"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="46">
+      <c r="A51" s="49">
         <v>1</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="48">
+      <c r="C51" s="46">
         <v>4</v>
       </c>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F51" s="21" t="s">
@@ -3615,7 +3614,7 @@
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
       <c r="D52" s="47"/>
-      <c r="E52" s="49"/>
+      <c r="E52" s="48"/>
       <c r="F52" s="27" t="s">
         <v>14</v>
       </c>
@@ -3653,19 +3652,19 @@
       <c r="AL52" s="30"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="46">
+      <c r="A53" s="49">
         <v>2</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B53" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="48">
+      <c r="C53" s="46">
         <v>4</v>
       </c>
-      <c r="D53" s="48" t="s">
+      <c r="D53" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F53" s="31" t="s">
@@ -3708,8 +3707,8 @@
       <c r="A54" s="47"/>
       <c r="B54" s="47"/>
       <c r="C54" s="47"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="49"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="48"/>
       <c r="F54" s="34" t="s">
         <v>14</v>
       </c>
@@ -3747,19 +3746,19 @@
       <c r="AL54" s="37"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="46">
+      <c r="A55" s="49">
         <v>3</v>
       </c>
-      <c r="B55" s="48" t="s">
+      <c r="B55" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="48">
+      <c r="C55" s="46">
         <v>2</v>
       </c>
-      <c r="D55" s="48" t="s">
+      <c r="D55" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="48" t="s">
+      <c r="E55" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F55" s="21" t="s">
@@ -3802,8 +3801,8 @@
       <c r="A56" s="47"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
       <c r="F56" s="38" t="s">
         <v>14</v>
       </c>
@@ -3841,19 +3840,19 @@
       <c r="AL56" s="30"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="46">
+      <c r="A57" s="49">
         <v>4</v>
       </c>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="48">
+      <c r="C57" s="46">
         <v>3</v>
       </c>
-      <c r="D57" s="48" t="s">
+      <c r="D57" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="46" t="s">
         <v>35</v>
       </c>
       <c r="F57" s="31" t="s">
@@ -3896,8 +3895,8 @@
       <c r="A58" s="47"/>
       <c r="B58" s="47"/>
       <c r="C58" s="47"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
       <c r="F58" s="34" t="s">
         <v>14</v>
       </c>
@@ -3935,13 +3934,13 @@
       <c r="AL58" s="37"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="46">
+      <c r="A59" s="49">
         <v>5</v>
       </c>
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
+      <c r="B59" s="46"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
       <c r="F59" s="21" t="s">
         <v>13</v>
       </c>
@@ -4021,13 +4020,13 @@
       <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="46">
+      <c r="A61" s="49">
         <v>6</v>
       </c>
-      <c r="B61" s="48"/>
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="46"/>
       <c r="F61" s="31" t="s">
         <v>13</v>
       </c>
@@ -4149,19 +4148,19 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="46">
+      <c r="A64" s="49">
         <v>1</v>
       </c>
-      <c r="B64" s="48" t="s">
+      <c r="B64" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="48">
+      <c r="C64" s="46">
         <v>2</v>
       </c>
-      <c r="D64" s="48" t="s">
+      <c r="D64" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="46" t="s">
         <v>38</v>
       </c>
       <c r="F64" s="21" t="s">
@@ -4243,13 +4242,13 @@
       <c r="AL65" s="30"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="46">
+      <c r="A66" s="49">
         <v>2</v>
       </c>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
+      <c r="B66" s="46"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
       <c r="F66" s="31" t="s">
         <v>13</v>
       </c>
@@ -4329,13 +4328,13 @@
       <c r="AL67" s="37"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="46">
+      <c r="A68" s="49">
         <v>3</v>
       </c>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
+      <c r="B68" s="46"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4415,13 +4414,13 @@
       <c r="AL69" s="30"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="46">
+      <c r="A70" s="49">
         <v>4</v>
       </c>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
+      <c r="B70" s="46"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
       <c r="F70" s="31" t="s">
         <v>13</v>
       </c>
@@ -4501,13 +4500,13 @@
       <c r="AL71" s="37"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="46">
+      <c r="A72" s="49">
         <v>5</v>
       </c>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
+      <c r="B72" s="46"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -4587,13 +4586,13 @@
       <c r="AL73" s="41"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="49">
         <v>6</v>
       </c>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
+      <c r="B74" s="46"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
       <c r="F74" s="31" t="s">
         <v>13</v>
       </c>
@@ -4713,13 +4712,13 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="46">
+      <c r="A77" s="49">
         <v>1</v>
       </c>
-      <c r="B77" s="48"/>
-      <c r="C77" s="48"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
+      <c r="B77" s="46"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="46"/>
+      <c r="E77" s="46"/>
       <c r="F77" s="21" t="s">
         <v>13</v>
       </c>
@@ -4799,13 +4798,13 @@
       <c r="AL78" s="30"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="46">
+      <c r="A79" s="49">
         <v>2</v>
       </c>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
+      <c r="B79" s="46"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
       <c r="F79" s="31" t="s">
         <v>13</v>
       </c>
@@ -4885,13 +4884,13 @@
       <c r="AL80" s="37"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="46">
+      <c r="A81" s="49">
         <v>3</v>
       </c>
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
+      <c r="B81" s="46"/>
+      <c r="C81" s="46"/>
+      <c r="D81" s="46"/>
+      <c r="E81" s="46"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -4971,13 +4970,13 @@
       <c r="AL82" s="30"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="46">
+      <c r="A83" s="49">
         <v>4</v>
       </c>
-      <c r="B83" s="48"/>
-      <c r="C83" s="48"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="48"/>
+      <c r="B83" s="46"/>
+      <c r="C83" s="46"/>
+      <c r="D83" s="46"/>
+      <c r="E83" s="46"/>
       <c r="F83" s="31" t="s">
         <v>13</v>
       </c>
@@ -41698,21 +41697,168 @@
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C29:C30"/>
@@ -41737,168 +41883,21 @@
     <mergeCell ref="D44:D45"/>
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">

--- a/進捗管理表_森数.xlsx
+++ b/進捗管理表_森数.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F64A686-C2D8-43C0-8371-9E72422517D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56C0AE26-0D4D-4676-9D59-F4C88A63E8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小工程" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2720,7 +2731,7 @@
       </c>
       <c r="G32" s="35"/>
       <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
+      <c r="I32" s="23"/>
       <c r="J32" s="36"/>
       <c r="K32" s="36"/>
       <c r="L32" s="36"/>
